--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10278\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB6AD59-03A0-4477-94B6-0290BEEA7588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB016EA-BFCB-4CE3-B495-12349217FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-29" sheetId="1" r:id="rId1"/>
@@ -114,12 +114,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,13 +438,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,9 +469,21 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="日期格式错误" sqref="A1:A1048576" xr:uid="{4196859D-5798-4DE8-AD66-DE3B403E42E8}">
+      <formula1>1</formula1>
+      <formula2>401769</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号最长18位！" sqref="G1:G1048576" xr:uid="{05278359-45BC-47AD-AE8E-A706100527CA}">
+      <formula1>18</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB016EA-BFCB-4CE3-B495-12349217FFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340B000D-423F-4BAD-B3BE-7500B0BCD2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -122,6 +122,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -441,7 +447,9 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.25" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -463,7 +471,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -480,7 +488,7 @@
       <formula1>1</formula1>
       <formula2>401769</formula2>
     </dataValidation>
-    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号最长18位！" sqref="G1:G1048576" xr:uid="{05278359-45BC-47AD-AE8E-A706100527CA}">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号应该为18位！" sqref="G1:G1048576" xr:uid="{05278359-45BC-47AD-AE8E-A706100527CA}">
       <formula1>18</formula1>
     </dataValidation>
   </dataValidations>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
@@ -8,24 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340B000D-423F-4BAD-B3BE-7500B0BCD2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870C0656-D870-4C43-BA5A-19E27EA39E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-29" sheetId="1" r:id="rId1"/>
+    <sheet name="2023-09-19" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>增加时间</t>
   </si>
   <si>
     <t>原序号</t>
+  </si>
+  <si>
+    <t>单位名称</t>
   </si>
   <si>
     <t>一般课题名称</t>
@@ -63,6 +66,7 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -114,21 +118,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,15 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="30.25" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="1" max="9" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,28 +464,23 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="日期格式错误" sqref="A1:A1048576" xr:uid="{4196859D-5798-4DE8-AD66-DE3B403E42E8}">
-      <formula1>1</formula1>
-      <formula2>401769</formula2>
-    </dataValidation>
-    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号应该为18位！" sqref="G1:G1048576" xr:uid="{05278359-45BC-47AD-AE8E-A706100527CA}">
+  <dataValidations count="1">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号为18位数字！" sqref="H1:H1048576" xr:uid="{F3E4A73D-0B89-4B8D-AD4F-E5181160F3AC}">
       <formula1>18</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchPatentDeclarePlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870C0656-D870-4C43-BA5A-19E27EA39E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C62E9B-FF30-4550-94E4-576E0AE8B127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,12 +118,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,7 +448,9 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="16.75" customWidth="1"/>
+    <col min="1" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -467,7 +475,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -477,7 +485,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号为18位数字！" sqref="H1:H1048576" xr:uid="{F3E4A73D-0B89-4B8D-AD4F-E5181160F3AC}">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="身份证号长度为18位！" sqref="H1:H1048576" xr:uid="{F3E4A73D-0B89-4B8D-AD4F-E5181160F3AC}">
       <formula1>18</formula1>
     </dataValidation>
   </dataValidations>
